--- a/Vulnerability Test Results/security_assessment_kisan_mitra.xlsx
+++ b/Vulnerability Test Results/security_assessment_kisan_mitra.xlsx
@@ -750,7 +750,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-22 10:50  |  Framework: FastAPI (Python 3.11)  |  Assessor: Senior AppSec Engineer</t>
+          <t>Generated: 2026-06-23 14:51  |  Framework: FastAPI (Python 3.11)  |  Assessor: Senior AppSec Engineer</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="J3" s="18" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="J5" s="18" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="J7" s="18" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="J9" s="18" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="J11" s="18" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -5665,9 +5665,9 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="G3" s="32" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G3" s="34" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H3" s="18" t="inlineStr"/>
@@ -5703,9 +5703,9 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="G4" s="32" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G4" s="34" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H4" s="21" t="inlineStr"/>
@@ -5741,9 +5741,9 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="G5" s="32" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G5" s="34" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H5" s="18" t="inlineStr"/>
@@ -5779,9 +5779,9 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="G6" s="32" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G6" s="34" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr"/>
@@ -5817,9 +5817,9 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="G7" s="32" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G7" s="34" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H7" s="18" t="inlineStr"/>
@@ -5855,9 +5855,9 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="G8" s="32" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G8" s="34" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr"/>
@@ -5893,9 +5893,9 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="G9" s="32" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G9" s="34" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H9" s="18" t="inlineStr"/>
@@ -5931,9 +5931,9 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="G10" s="32" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G10" s="34" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr"/>
@@ -5969,9 +5969,9 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="G11" s="32" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G11" s="34" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H11" s="18" t="inlineStr"/>
